--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
@@ -39,97 +39,97 @@
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelluhue</t>
+    <t xml:space="preserve">Hualañé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeral</t>
+    <t xml:space="preserve">Licantén</t>
   </si>
   <si>
     <t xml:space="preserve">Curepto</t>
   </si>
   <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
+    <t xml:space="preserve">Chanco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -553,16 +553,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7105</v>
+        <v>7403</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4392</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="3">
@@ -570,16 +570,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7403</v>
+        <v>7401</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4321</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>7404</v>
@@ -596,7 +596,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2568</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="5">
@@ -604,16 +604,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7402</v>
+        <v>7406</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1939</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="6">
@@ -621,16 +621,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7101</v>
+        <v>7304</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1936</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="7">
@@ -638,7 +638,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>7109</v>
@@ -647,7 +647,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1845</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="8">
@@ -655,16 +655,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7406</v>
+        <v>7306</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1776</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="9">
@@ -672,16 +672,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7203</v>
+        <v>7108</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1244</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="10">
@@ -689,16 +689,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7405</v>
+        <v>7105</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1163</v>
+        <v>955</v>
       </c>
     </row>
     <row r="11">
@@ -709,13 +709,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7408</v>
+        <v>7110</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1152</v>
+        <v>946</v>
       </c>
     </row>
     <row r="12">
@@ -726,13 +726,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7108</v>
+        <v>7301</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1110</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13">
@@ -743,13 +743,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7407</v>
+        <v>7402</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1049</v>
+        <v>892</v>
       </c>
     </row>
     <row r="14">
@@ -766,7 +766,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>991</v>
+        <v>845</v>
       </c>
     </row>
     <row r="15">
@@ -777,13 +777,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7201</v>
+        <v>7102</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>965</v>
+        <v>843</v>
       </c>
     </row>
     <row r="16">
@@ -794,13 +794,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7401</v>
+        <v>7308</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>886</v>
+        <v>817</v>
       </c>
     </row>
     <row r="17">
@@ -811,13 +811,13 @@
         <v>20</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7301</v>
+        <v>7203</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>872</v>
+        <v>782</v>
       </c>
     </row>
     <row r="18">
@@ -828,13 +828,13 @@
         <v>21</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7306</v>
+        <v>7307</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>795</v>
+        <v>773</v>
       </c>
     </row>
     <row r="19">
@@ -845,13 +845,13 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7103</v>
+        <v>7408</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>590</v>
+        <v>652</v>
       </c>
     </row>
     <row r="20">
@@ -862,13 +862,13 @@
         <v>23</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7308</v>
+        <v>7407</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>566</v>
+        <v>649</v>
       </c>
     </row>
     <row r="21">
@@ -879,13 +879,13 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7307</v>
+        <v>7101</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>524</v>
+        <v>611</v>
       </c>
     </row>
     <row r="22">
@@ -902,7 +902,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>485</v>
+        <v>607</v>
       </c>
     </row>
     <row r="23">
@@ -913,13 +913,13 @@
         <v>26</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7304</v>
+        <v>7107</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>437</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24">
@@ -930,13 +930,13 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7309</v>
+        <v>7201</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>328</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25">
@@ -947,13 +947,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7305</v>
+        <v>7405</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>325</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26">
@@ -964,13 +964,13 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7110</v>
+        <v>7303</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>311</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27">
@@ -981,13 +981,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7303</v>
+        <v>7103</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>288</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28">
@@ -998,13 +998,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7202</v>
+        <v>7309</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>175</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
@@ -1015,13 +1015,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>7104</v>
+        <v>7202</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-16</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30">
@@ -1032,13 +1032,13 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>7107</v>
+        <v>7305</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
@@ -1049,13 +1049,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7102</v>
+        <v>7104</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-118</v>
+        <v>-142</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:23</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-05 07:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
